--- a/output/pdf_financials_xlsx/NIO.xlsx
+++ b/output/pdf_financials_xlsx/NIO.xlsx
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.164161</v>
+        <v>0.385994</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.138164</v>
+        <v>0.498638</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.071607</v>
+        <v>0.330624</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.08801200000000001</v>
+        <v>0.298155</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.089255</v>
+        <v>0.244708</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0.740467</v>
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.156161</v>
+        <v>-0.377994</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.131664</v>
+        <v>-0.492138</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.06436500000000001</v>
+        <v>-0.323382</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.077212</v>
+        <v>-0.287355</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.07810499999999999</v>
+        <v>-0.233558</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-0.732667</v>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00067</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -840,13 +840,13 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.047704</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.037077</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.020166</v>
       </c>
     </row>
     <row r="13">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.5421550000000001</v>
+        <v>-0.541485</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.630302</v>
@@ -1495,13 +1495,13 @@
         <v>-0.477198</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.7292920000000001</v>
+        <v>-0.681588</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.8698090000000001</v>
+        <v>-0.832732</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.008878</v>
+        <v>-0.988712</v>
       </c>
     </row>
     <row r="28">
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.5421550000000001</v>
+        <v>-0.541485</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.630302</v>
@@ -1569,13 +1569,13 @@
         <v>-0.477198</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.7292920000000001</v>
+        <v>-0.681588</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.8698090000000001</v>
+        <v>-0.832732</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.008878</v>
+        <v>-0.988712</v>
       </c>
     </row>
     <row r="30">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-6776.9375</v>
+        <v>-6768.5625</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>-9696.953846153847</v>
@@ -1606,13 +1606,13 @@
         <v>-4161.126613184513</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-6027.206611570248</v>
+        <v>-5632.958677685951</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-10233.04705882353</v>
+        <v>-9796.847058823529</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-15286.0303030303</v>
+        <v>-14980.48484848485</v>
       </c>
     </row>
     <row r="31">
@@ -1718,7 +1718,7 @@
         <v>0.028895</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.943289</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>1.636519</v>
@@ -1792,7 +1792,7 @@
         <v>0.028895</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.943289</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>1.636519</v>
@@ -2236,7 +2236,7 @@
         <v>0.030625</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.14436</v>
+        <v>0.201071</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.081508</v>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -16920,7 +16920,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -22782,7 +22782,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E267" s="5" t="n">
@@ -24664,7 +24664,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E296" s="5" t="n">
@@ -24732,7 +24732,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E297" s="5" t="n">

--- a/output/pdf_financials_xlsx/NIO.xlsx
+++ b/output/pdf_financials_xlsx/NIO.xlsx
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.164161</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.138164</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.175518</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.201347</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.220345</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>-0</v>
@@ -1474,19 +1474,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.541485</v>
+        <v>-0.377324</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.630302</v>
+        <v>-0.492138</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.450326</v>
+        <v>-0.274808</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2e-06</v>
+        <v>0.201345</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2e-06</v>
+        <v>0.220343</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.99102</v>
@@ -1548,19 +1548,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.541485</v>
+        <v>-0.377324</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.630302</v>
+        <v>-0.492138</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.450326</v>
+        <v>-0.274808</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2e-06</v>
+        <v>0.201345</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2e-06</v>
+        <v>0.220343</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.99102</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-6768.5625</v>
+        <v>-4716.55</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-9696.953846153847</v>
+        <v>-7571.353846153846</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-6218.254625793979</v>
+        <v>-3794.642363987849</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-0.01851851851851852</v>
+        <v>1864.305555555556</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-0.0179372197309417</v>
+        <v>1976.170403587444</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-12705.38461538462</v>
@@ -21756,7 +21756,11 @@
           <t>Net finance expense 6,13</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -23042,7 +23046,11 @@
           <t>Net finance expenses</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -24014,7 +24022,11 @@
           <t>Net finance expenses</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -24402,7 +24414,11 @@
           <t>Net finance expenses 4</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E292" s="5" t="n">
         <v>0.164161</v>
       </c>

--- a/output/pdf_financials_xlsx/NIO.xlsx
+++ b/output/pdf_financials_xlsx/NIO.xlsx
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.133671</v>
+        <v>0.163526</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.073493</v>
+        <v>0.105245</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.071607</v>
+        <v>0.105666</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.08801200000000001</v>
+        <v>0.120532</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.089255</v>
+        <v>0.121782</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.095114</v>
+        <v>0.116716</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.109902</v>
+        <v>0.145478</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0.122396</v>
@@ -2833,19 +2833,19 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.014291</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.011815</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.050979</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.066898</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0</v>
@@ -2944,16 +2944,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.02522</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.225453</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.025493</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.046928</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0</v>
@@ -13234,7 +13234,11 @@
           <t>Issuance of units under a private placement 10</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -19310,7 +19314,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -21044,7 +21052,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E240" s="5" t="n">
         <v>0.029855</v>
       </c>
